--- a/stories/arbres/TREE-DIF-043.xlsx
+++ b/stories/arbres/TREE-DIF-043.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Hugo est avec papa, au parc. Hugo a envie de jouer. papa est là, tout près. On va apprendre : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo écoute papa. Hugo entend les mots : corps pas une blague, jouer.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers la cuisine. Il y a des miettes sur la table. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Hugo se souvient : corps pas une blague, jouer. Voici le geste : jouer ; pas commenter le corps. On souffle doucement. papa dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers la cuisine. Il y a des miettes sur la table. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Hugo se souvient : corps pas une blague, jouer. Voici le geste : jouer ; pas commenter le corps. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers la cuisine. Il y a des miettes sur la table. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Hugo se souvient : corps pas une blague, jouer. Voici le geste : jouer ; pas commenter le corps. On souffle doucement.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Plus rond ou plus mince.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; pas commenter le corps. Hugo respire. Hugo retient : corps pas une blague, jouer. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Hugo répète tout bas : corps pas une blague, jouer. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2580,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2747,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et le matin. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2914,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3081,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3248,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3415,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et le soir. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3582,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3749,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Hugo répète tout bas : corps pas une blague, jouer. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3940,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4107,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Le vent est doux. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et le matin. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4274,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4441,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et après la sieste. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4608,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4775,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. Une feuille tombe. On attend son tour. Cette fin-là est celle de la cuisine, le livre et le soir. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4942,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5109,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Hugo répète tout bas : corps pas une blague, jouer. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5300,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5467,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et le matin. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5634,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5801,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5968,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6135,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et le soir. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6302,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6163,7 +6331,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers le jardin. Un chat miaule une fois. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Hugo se souvient : corps pas une blague, jouer. Voici le geste : jouer ; pas commenter le corps. On écoute jusqu'au bout. papa dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers le jardin. Un chat miaule une fois. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Hugo se souvient : corps pas une blague, jouer. Voici le geste : jouer ; pas commenter le corps. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6301,6 +6469,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers le jardin. Un chat miaule une fois. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Hugo se souvient : corps pas une blague, jouer. Voici le geste : jouer ; pas commenter le corps. On écoute jusqu'au bout.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6651,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Plus rond ou plus mince.</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6824,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; pas commenter le corps. Hugo respire. Hugo retient : corps pas une blague, jouer. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7015,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7182,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi les cubes. Ça sent le pain chaud. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Hugo répète tout bas : corps pas une blague, jouer. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7373,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7540,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et le matin. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7707,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7874,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le jardin, les cubes et après la sieste. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8041,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8208,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et le soir. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8375,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8542,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le livre. Le vent est doux. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Hugo répète tout bas : corps pas une blague, jouer. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8733,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8900,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et le matin. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9067,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9234,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. Une feuille tombe. On attend son tour. Cette fin-là est celle de le jardin, le livre et après la sieste. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9401,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9568,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et le soir. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9735,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9902,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi la dînette. Le sol est un peu froid. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Hugo répète tout bas : corps pas une blague, jouer. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10093,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10260,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et le matin. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10427,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10594,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le jardin, la dînette et après la sieste. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10761,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10928,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et le soir. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11095,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10815,7 +11124,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Hugo va vers la chambre. Les chaussures font toc toc. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Hugo se souvient : corps pas une blague, jouer. Voici le geste : jouer ; pas commenter le corps. On attend son tour. papa dit : je suis là. On reste ensemble.</t>
+          <t>Hugo va vers la chambre. Les chaussures font toc toc. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Hugo se souvient : corps pas une blague, jouer. Voici le geste : jouer ; pas commenter le corps. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10953,6 +11262,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo va vers la chambre. Les chaussures font toc toc. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Hugo se souvient : corps pas une blague, jouer. Voici le geste : jouer ; pas commenter le corps. On attend son tour.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11444,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Plus rond ou plus mince.</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11617,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : jouer ; pas commenter le corps. Hugo respire. Hugo retient : corps pas une blague, jouer. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11808,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11975,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Hugo répète tout bas : corps pas une blague, jouer. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12166,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12333,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la chambre, les cubes et le matin. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12500,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12667,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et après la sieste. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12834,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13001,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la chambre, les cubes et le soir. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13168,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13335,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Hugo répète tout bas : corps pas une blague, jouer. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13526,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13693,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. Une feuille tombe. On attend son tour. Cette fin-là est celle de la chambre, le livre et le matin. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13860,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14027,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et après la sieste. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14194,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14361,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la chambre, le livre et le soir. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14528,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14695,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Hugo répète tout bas : corps pas une blague, jouer. On se tait une seconde. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14886,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15053,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le matin. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la chambre, la dînette et le matin. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15220,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15387,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint après la sieste. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et après la sieste. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15554,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15721,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo rejoint le soir. La lumière est claire. On rit un peu. Cette fin-là est celle de la chambre, la dînette et le soir. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15888,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15928,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-043.xlsx
+++ b/stories/arbres/TREE-DIF-043.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,11 @@
           <t>narrateur|Aujourd'hui, Hugo est avec papa, au parc. Hugo a envie de jouer. papa est là, tout près. On va apprendre : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo écoute papa. Hugo entend les mots : corps pas une blague, jouer.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1524,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1693,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Plus rond ou plus mince.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; pas commenter le corps. Hugo respire. Hugo retient : corps pas une blague, jouer. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2241,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2409,7 @@
           <t>narrateur|Hugo a choisi les cubes. Les chaussures font toc toc. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Hugo répète tout bas : corps pas une blague, jouer. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2585,6 +2601,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2752,6 +2769,7 @@
           <t>narrateur|Hugo rejoint le matin. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et le matin. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2919,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3086,6 +3105,7 @@
           <t>narrateur|Hugo rejoint après la sieste. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3253,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3420,6 +3441,7 @@
           <t>narrateur|Hugo rejoint le soir. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la cuisine, les cubes et le soir. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3587,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3754,6 +3777,7 @@
           <t>narrateur|Hugo a choisi le livre. La couverture est douce. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Hugo répète tout bas : corps pas une blague, jouer. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3945,6 +3969,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4112,6 +4137,7 @@
           <t>narrateur|Hugo rejoint le matin. Le vent est doux. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et le matin. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4279,6 +4305,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4446,6 +4473,7 @@
           <t>narrateur|Hugo rejoint après la sieste. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et après la sieste. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4613,6 +4641,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4780,6 +4809,7 @@
           <t>narrateur|Hugo rejoint le soir. Une feuille tombe. On attend son tour. Cette fin-là est celle de la cuisine, le livre et le soir. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4947,6 +4977,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5114,6 +5145,7 @@
           <t>narrateur|Hugo a choisi la dînette. On entend un oiseau. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Hugo répète tout bas : corps pas une blague, jouer. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5305,6 +5337,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5472,6 +5505,7 @@
           <t>narrateur|Hugo rejoint le matin. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et le matin. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5639,6 +5673,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5806,6 +5841,7 @@
           <t>narrateur|Hugo rejoint après la sieste. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5973,6 +6009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6140,6 +6177,7 @@
           <t>narrateur|Hugo rejoint le soir. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la cuisine, la dînette et le soir. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6307,6 +6345,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6514,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6698,7 @@
           <t>narrateur|Que fait-on ? Plus rond ou plus mince.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6829,6 +6870,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; pas commenter le corps. Hugo respire. Hugo retient : corps pas une blague, jouer. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7020,6 +7062,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7187,6 +7230,7 @@
           <t>narrateur|Hugo a choisi les cubes. Ça sent le pain chaud. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Hugo répète tout bas : corps pas une blague, jouer. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7378,6 +7422,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7545,6 +7590,7 @@
           <t>narrateur|Hugo rejoint le matin. Le vent est doux. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et le matin. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7712,6 +7758,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7879,6 +7926,7 @@
           <t>narrateur|Hugo rejoint après la sieste. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de le jardin, les cubes et après la sieste. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8046,6 +8094,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8213,6 +8262,7 @@
           <t>narrateur|Hugo rejoint le soir. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, les cubes et le soir. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8380,6 +8430,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8547,6 +8598,7 @@
           <t>narrateur|Hugo a choisi le livre. Le vent est doux. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Hugo répète tout bas : corps pas une blague, jouer. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8738,6 +8790,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8905,6 +8958,7 @@
           <t>narrateur|Hugo rejoint le matin. Le sol est un peu froid. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et le matin. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9072,6 +9126,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9239,6 +9294,7 @@
           <t>narrateur|Hugo rejoint après la sieste. Une feuille tombe. On attend son tour. Cette fin-là est celle de le jardin, le livre et après la sieste. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9406,6 +9462,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9573,6 +9630,7 @@
           <t>narrateur|Hugo rejoint le soir. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, le livre et le soir. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9740,6 +9798,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9907,6 +9966,7 @@
           <t>narrateur|Hugo a choisi la dînette. Le sol est un peu froid. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Hugo répète tout bas : corps pas une blague, jouer. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10098,6 +10158,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10265,6 +10326,7 @@
           <t>narrateur|Hugo rejoint le matin. Une feuille tombe. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et le matin. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10432,6 +10494,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10599,6 +10662,7 @@
           <t>narrateur|Hugo rejoint après la sieste. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de le jardin, la dînette et après la sieste. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10766,6 +10830,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10933,6 +10998,7 @@
           <t>narrateur|Hugo rejoint le soir. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de le jardin, la dînette et le soir. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11100,6 +11166,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11268,6 +11335,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11451,6 +11519,7 @@
           <t>narrateur|Que fait-on ? Plus rond ou plus mince.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11622,6 +11691,7 @@
           <t>narrateur|Oui. Voici le geste : jouer ; pas commenter le corps. Hugo respire. Hugo retient : corps pas une blague, jouer. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11813,6 +11883,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11980,6 +12051,7 @@
           <t>narrateur|Hugo a choisi les cubes. Une feuille tombe. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Hugo répète tout bas : corps pas une blague, jouer. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12171,6 +12243,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12338,6 +12411,7 @@
           <t>narrateur|Hugo rejoint le matin. Le sol est un peu froid. On attend son tour. Cette fin-là est celle de la chambre, les cubes et le matin. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12505,6 +12579,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12672,6 +12747,7 @@
           <t>narrateur|Hugo rejoint après la sieste. Une feuille tombe. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et après la sieste. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12839,6 +12915,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13006,6 +13083,7 @@
           <t>narrateur|Hugo rejoint le soir. L'eau coule, tout petit bruit. On rit un peu. Cette fin-là est celle de la chambre, les cubes et le soir. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13173,6 +13251,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13340,6 +13419,7 @@
           <t>narrateur|Hugo a choisi le livre. L'eau coule, tout petit bruit. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Hugo répète tout bas : corps pas une blague, jouer. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13531,6 +13611,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13698,6 +13779,7 @@
           <t>narrateur|Hugo rejoint le matin. Une feuille tombe. On attend son tour. Cette fin-là est celle de la chambre, le livre et le matin. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13865,6 +13947,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14032,6 +14115,7 @@
           <t>narrateur|Hugo rejoint après la sieste. L'eau coule, tout petit bruit. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et après la sieste. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14199,6 +14283,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14366,6 +14451,7 @@
           <t>narrateur|Hugo rejoint le soir. Un vélo passe au loin. On rit un peu. Cette fin-là est celle de la chambre, le livre et le soir. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14533,6 +14619,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14700,6 +14787,7 @@
           <t>narrateur|Hugo a choisi la dînette. Un vélo passe au loin. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : jouer ; pas commenter le corps. Hugo répète tout bas : corps pas une blague, jouer. On se tait une seconde. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14891,6 +14979,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15058,6 +15147,7 @@
           <t>narrateur|Hugo rejoint le matin. L'eau coule, tout petit bruit. On attend son tour. Cette fin-là est celle de la chambre, la dînette et le matin. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15225,6 +15315,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15392,6 +15483,7 @@
           <t>narrateur|Hugo rejoint après la sieste. Un vélo passe au loin. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et après la sieste. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15559,6 +15651,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15726,6 +15819,7 @@
           <t>narrateur|Hugo rejoint le soir. La lumière est claire. On rit un peu. Cette fin-là est celle de la chambre, la dînette et le soir. Hugo a appris : Plus rond ou plus mince. Voici le geste : jouer ; pas commenter le corps. Hugo a entendu : corps pas une blague, jouer. Hugo dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15893,6 +15987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15911,7 +16006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15935,6 +16030,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15949,7 +16058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16136,6 +16245,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-043.xlsx
+++ b/stories/arbres/TREE-DIF-043.xlsx
@@ -1197,12 +1197,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sous les tilleuls, le parc sent l'herbe. Une mare brille, toute plate. Des feuilles sèches font un bruit, tout sec. Papa pose le sac, près du banc. Maman tient le seau, encore vide. Deux canards avancent, l'un derrière l'autre. Le premier a le ventre tout rond. Le second a le cou tout mince. Tu les as vus, Nino ? Oui, les deux. Je veux leur donner à manger. Les deux, Nino ? Les deux. En ce moment, Nino touche le pain. La croûte est un peu rêche, encore. Ils ne se ressemblent pas. On donne aux deux. Le pain, la nappe, et le seau. Merci, tu as vu les deux. On prépare, d'abord.</t>
+          <t>Sous les tilleuls, le parc sent l'herbe. Tu sens l'herbe, Nino ? Oui, elle est chaude. Une mare brille, toute plate. Elle est calme, là. Des feuilles sèches font un bruit, tout sec. Toc toc, les feuilles. Papa pose le sac, près du banc. Le seau est encore vide. Deux canards avancent, l'un derrière l'autre. Tu les as vus, Nino ? Oui, les deux. Le premier a le ventre tout rond. Le second a le cou tout mince. Je veux leur donner à manger. Les deux, Nino ? Les deux. En ce moment, Nino touche le pain. La croûte est un peu rêche, encore. Ils ne se ressemblent pas. On donne aux deux. Le pain, la nappe, et le seau. Merci, tu as vu les deux. On prépare, d'abord.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Sous les tilleuls, le parc sent l'herbe. Une mare brille, toute plate. Des feuilles sèches font un bruit, tout sec. Papa pose le sac, près du banc. Maman tient le seau, encore vide. Deux canards avancent, l'un derrière l'autre. Le premier a le ventre tout rond. Le second a le cou tout mince. Tu les as vus, Nino ? Oui, les deux. Je veux leur donner à manger. Les deux, Nino ? Les deux. En ce moment, Nino touche le pain. La croûte est un peu rêche, encore. Ils ne se ressemblent pas. On donne aux deux. Le pain, la nappe, et le seau. Merci, tu as vu les deux. On prépare, d'abord.</t>
+          <t>Sous les tilleuls, le parc sent l'herbe. Tu sens l'herbe, Nino ? Oui, elle est chaude. Une mare brille, toute plate. Elle est calme, là. Des feuilles sèches font un bruit, tout sec. Toc toc, les feuilles. Papa pose le sac, près du banc. Le seau est encore vide. Deux canards avancent, l'un derrière l'autre. Tu les as vus, Nino ? Oui, les deux. Le premier a le ventre tout rond. Le second a le cou tout mince. Je veux leur donner à manger. Les deux, Nino ? Les deux. En ce moment, Nino touche le pain. La croûte est un peu rêche, encore. Ils ne se ressemblent pas. On donne aux deux. Le pain, la nappe, et le seau. Merci, tu as vu les deux. On prépare, d'abord.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1338,15 +1338,19 @@
       <c r="AW2" t="inlineStr">
         <is>
           <t>narrateur|Sous les tilleuls, le parc sent l'herbe.
+papa|Tu sens l'herbe, Nino ?
+enfant-m|Oui, elle est chaude.
 narrateur|Une mare brille, toute plate.
+maman|Elle est calme, là.
 narrateur|Des feuilles sèches font un bruit, tout sec.
+enfant-m|Toc toc, les feuilles.
 narrateur|Papa pose le sac, près du banc.
-narrateur|Maman tient le seau, encore vide.
+maman|Le seau est encore vide.
 narrateur|Deux canards avancent, l'un derrière l'autre.
+papa|Tu les as vus, Nino ?
+enfant-m|Oui, les deux.
 narrateur|Le premier a le ventre tout rond.
 narrateur|Le second a le cou tout mince.
-papa|Tu les as vus, Nino ?
-enfant-m|Oui, les deux.
 enfant-m|Je veux leur donner à manger.
 papa|Les deux, Nino ?
 enfant-m|Les deux.
@@ -2314,12 +2318,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Le pain sent encore le four, tout chaud. Ils s'approchent de la mare, trop haute. Un morceau de pain tombe, trop loin. L'eau fait un pli, trop vif. Vous venez. Le canard rond reste au bord. Le mince part, trop léger, trop loin. L'un reste, l'autre part. Ils n'ont pas la même forme. Tu fais quoi, avec les deux ?</t>
+          <t>Le pain sent encore le four, tout chaud. Ils s'approchent de la mare, trop haute. L'eau est grande. Un morceau de pain tombe, trop loin. L'eau fait un pli, trop vif. Vous venez. Le canard rond reste au bord. Le mince part, trop léger, trop loin. L'un reste, l'autre part. Ils n'ont pas la même forme. Tu fais quoi, avec les deux ?</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Le pain sent encore le four, tout chaud. Ils s'approchent de la mare, trop haute. Un morceau de pain tombe, trop loin. L'eau fait un pli, trop vif. Vous venez. Le canard rond reste au bord. Le mince part, trop léger, trop loin. L'un reste, l'autre part. Ils n'ont pas la même forme. Tu fais quoi, avec les deux ?</t>
+          <t>Le pain sent encore le four, tout chaud. Ils s'approchent de la mare, trop haute. L'eau est grande. Un morceau de pain tombe, trop loin. L'eau fait un pli, trop vif. Vous venez. Le canard rond reste au bord. Le mince part, trop léger, trop loin. L'un reste, l'autre part. Ils n'ont pas la même forme. Tu fais quoi, avec les deux ?</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2456,6 +2460,7 @@
         <is>
           <t>narrateur|Le pain sent encore le four, tout chaud.
 narrateur|Ils s'approchent de la mare, trop haute.
+enfant-m|L'eau est grande.
 narrateur|Un morceau de pain tombe, trop loin.
 narrateur|L'eau fait un pli, trop vif.
 enfant-m|Vous venez.
@@ -3731,12 +3736,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Le pain sent encore le four, tout chaud. Sur le banc, les planches ont des fentes. Des miettes tombent entre les planches. Le goûter, ici. Nino s'assoit, trop haut pour eux. Le canard rond bute, trop large. Le mince glisse entre les planches. Ce n'est pas juste. Le banc a des trous, voilà tout. Tu les gardes comment, ensemble ?</t>
+          <t>Le pain sent encore le four, tout chaud. Sur le banc, les planches ont des fentes. Le goûter, ici. Des miettes tombent entre les planches. Nino s'assoit, trop haut pour eux. Tu es trop haut, pour eux. Le canard rond bute, trop large. Le mince glisse entre les planches. Ce n'est pas juste. Le banc a des trous, voilà tout. Tu les gardes comment, ensemble ?</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Le pain sent encore le four, tout chaud. Sur le banc, les planches ont des fentes. Des miettes tombent entre les planches. Le goûter, ici. Nino s'assoit, trop haut pour eux. Le canard rond bute, trop large. Le mince glisse entre les planches. Ce n'est pas juste. Le banc a des trous, voilà tout. Tu les gardes comment, ensemble ?</t>
+          <t>Le pain sent encore le four, tout chaud. Sur le banc, les planches ont des fentes. Le goûter, ici. Des miettes tombent entre les planches. Nino s'assoit, trop haut pour eux. Tu es trop haut, pour eux. Le canard rond bute, trop large. Le mince glisse entre les planches. Ce n'est pas juste. Le banc a des trous, voilà tout. Tu les gardes comment, ensemble ?</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3873,9 +3878,10 @@
         <is>
           <t>narrateur|Le pain sent encore le four, tout chaud.
 narrateur|Sur le banc, les planches ont des fentes.
+enfant-m|Le goûter, ici.
 narrateur|Des miettes tombent entre les planches.
-enfant-m|Le goûter, ici.
 narrateur|Nino s'assoit, trop haut pour eux.
+papa|Tu es trop haut, pour eux.
 narrateur|Le canard rond bute, trop large.
 narrateur|Le mince glisse entre les planches.
 enfant-m|Ce n'est pas juste.
@@ -4104,12 +4110,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>L'herbe, comme une table. Il pose le pain dans l'herbe, tout bas. Nino s'assoit, les pieds dans l'herbe. Le canard rond s'assoit, trop rond. Le mince s'allonge contre lui, trop mince. Vous avez le sol, tous les deux. Chacun a sa place. Un peu de croûte reste, tout rêche. Les miettes restent, plus calmes.</t>
+          <t>L'herbe, comme une table. Il pose le pain dans l'herbe, tout bas. Nino s'assoit, les pieds dans l'herbe. Tout doux, dans l'herbe. Le canard rond s'assoit, trop rond. Le mince s'allonge contre lui, trop mince. Vous avez le sol, tous les deux. Chacun a sa place. Un peu de croûte reste, tout rêche. Les miettes restent, plus calmes.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>L'herbe, comme une table. Il pose le pain dans l'herbe, tout bas. Nino s'assoit, les pieds dans l'herbe. Le canard rond s'assoit, trop rond. Le mince s'allonge contre lui, trop mince. Vous avez le sol, tous les deux. Chacun a sa place. Un peu de croûte reste, tout rêche. Les miettes restent, plus calmes.</t>
+          <t>L'herbe, comme une table. Il pose le pain dans l'herbe, tout bas. Nino s'assoit, les pieds dans l'herbe. Tout doux, dans l'herbe. Le canard rond s'assoit, trop rond. Le mince s'allonge contre lui, trop mince. Vous avez le sol, tous les deux. Chacun a sa place. Un peu de croûte reste, tout rêche. Les miettes restent, plus calmes.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4247,6 +4253,7 @@
           <t>enfant-m|L'herbe, comme une table.
 narrateur|Il pose le pain dans l'herbe, tout bas.
 narrateur|Nino s'assoit, les pieds dans l'herbe.
+papa|Tout doux, dans l'herbe.
 narrateur|Le canard rond s'assoit, trop rond.
 narrateur|Le mince s'allonge contre lui, trop mince.
 enfant-m|Vous avez le sol, tous les deux.
@@ -5147,12 +5154,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Le pain sent encore le four, tout chaud. Au kiosque, les marches sont trop hautes. Le pain sent encore, trop loin de l'eau. Le goûter, là-haut. Un vent passe, tout froid. Le canard rond ne monte pas. Le mince commence, puis recule. Ils ne viennent pas. Le kiosque est trop loin de l'eau. Tu les rassembles comment ?</t>
+          <t>Le pain sent encore le four, tout chaud. Au kiosque, les marches sont trop hautes. Le goûter, là-haut. Le pain sent encore, trop loin de l'eau. Un vent passe, tout froid. Trop haut, trop loin. Le canard rond ne monte pas. Le mince commence, puis recule. Ils ne viennent pas. Le kiosque est trop loin de l'eau. Tu les rassembles comment ?</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Le pain sent encore le four, tout chaud. Au kiosque, les marches sont trop hautes. Le pain sent encore, trop loin de l'eau. Le goûter, là-haut. Un vent passe, tout froid. Le canard rond ne monte pas. Le mince commence, puis recule. Ils ne viennent pas. Le kiosque est trop loin de l'eau. Tu les rassembles comment ?</t>
+          <t>Le pain sent encore le four, tout chaud. Au kiosque, les marches sont trop hautes. Le goûter, là-haut. Le pain sent encore, trop loin de l'eau. Un vent passe, tout froid. Trop haut, trop loin. Le canard rond ne monte pas. Le mince commence, puis recule. Ils ne viennent pas. Le kiosque est trop loin de l'eau. Tu les rassembles comment ?</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5289,9 +5296,10 @@
         <is>
           <t>narrateur|Le pain sent encore le four, tout chaud.
 narrateur|Au kiosque, les marches sont trop hautes.
+enfant-m|Le goûter, là-haut.
 narrateur|Le pain sent encore, trop loin de l'eau.
-enfant-m|Le goûter, là-haut.
 narrateur|Un vent passe, tout froid.
+maman|Trop haut, trop loin.
 narrateur|Le canard rond ne monte pas.
 narrateur|Le mince commence, puis recule.
 enfant-m|Ils ne viennent pas.
@@ -7295,12 +7303,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Un coin de nappe frotte l'herbe. Ils s'approchent de la mare, trop haute. La nappe accroche l'herbe, puis lâche. L'eau fait un pli, trop vif. Vous venez. Le canard rond reste au bord. Le mince part, trop léger, trop loin. L'un reste, l'autre part. Ils n'ont pas la même forme. Tu fais quoi, avec les deux ?</t>
+          <t>Un coin de nappe frotte l'herbe. Ils s'approchent de la mare, trop haute. L'eau est grande. La nappe accroche l'herbe, puis lâche. L'eau fait un pli, trop vif. Vous venez. Le canard rond reste au bord. Le mince part, trop léger, trop loin. L'un reste, l'autre part. Ils n'ont pas la même forme. Tu fais quoi, avec les deux ?</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Un coin de nappe frotte l'herbe. Ils s'approchent de la mare, trop haute. La nappe accroche l'herbe, puis lâche. L'eau fait un pli, trop vif. Vous venez. Le canard rond reste au bord. Le mince part, trop léger, trop loin. L'un reste, l'autre part. Ils n'ont pas la même forme. Tu fais quoi, avec les deux ?</t>
+          <t>Un coin de nappe frotte l'herbe. Ils s'approchent de la mare, trop haute. L'eau est grande. La nappe accroche l'herbe, puis lâche. L'eau fait un pli, trop vif. Vous venez. Le canard rond reste au bord. Le mince part, trop léger, trop loin. L'un reste, l'autre part. Ils n'ont pas la même forme. Tu fais quoi, avec les deux ?</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -7437,6 +7445,7 @@
         <is>
           <t>narrateur|Un coin de nappe frotte l'herbe.
 narrateur|Ils s'approchent de la mare, trop haute.
+enfant-m|L'eau est grande.
 narrateur|La nappe accroche l'herbe, puis lâche.
 narrateur|L'eau fait un pli, trop vif.
 enfant-m|Vous venez.
@@ -8712,12 +8721,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Un coin de nappe frotte l'herbe. Sur le banc, les planches ont des fentes. La nappe glisse dans le vide, trop mince. Le goûter, ici. Nino s'assoit, trop haut pour eux. Le canard rond bute, trop large. Le mince glisse entre les planches. Ce n'est pas juste. Le banc a des trous, voilà tout. Tu les gardes comment, ensemble ?</t>
+          <t>Un coin de nappe frotte l'herbe. Sur le banc, les planches ont des fentes. Le goûter, ici. La nappe glisse dans le vide, trop mince. Nino s'assoit, trop haut pour eux. Tu es trop haut, pour eux. Le canard rond bute, trop large. Le mince glisse entre les planches. Ce n'est pas juste. Le banc a des trous, voilà tout. Tu les gardes comment, ensemble ?</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Un coin de nappe frotte l'herbe. Sur le banc, les planches ont des fentes. La nappe glisse dans le vide, trop mince. Le goûter, ici. Nino s'assoit, trop haut pour eux. Le canard rond bute, trop large. Le mince glisse entre les planches. Ce n'est pas juste. Le banc a des trous, voilà tout. Tu les gardes comment, ensemble ?</t>
+          <t>Un coin de nappe frotte l'herbe. Sur le banc, les planches ont des fentes. Le goûter, ici. La nappe glisse dans le vide, trop mince. Nino s'assoit, trop haut pour eux. Tu es trop haut, pour eux. Le canard rond bute, trop large. Le mince glisse entre les planches. Ce n'est pas juste. Le banc a des trous, voilà tout. Tu les gardes comment, ensemble ?</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -8854,9 +8863,10 @@
         <is>
           <t>narrateur|Un coin de nappe frotte l'herbe.
 narrateur|Sur le banc, les planches ont des fentes.
+enfant-m|Le goûter, ici.
 narrateur|La nappe glisse dans le vide, trop mince.
-enfant-m|Le goûter, ici.
 narrateur|Nino s'assoit, trop haut pour eux.
+papa|Tu es trop haut, pour eux.
 narrateur|Le canard rond bute, trop large.
 narrateur|Le mince glisse entre les planches.
 enfant-m|Ce n'est pas juste.
@@ -9085,12 +9095,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>L'herbe, comme une table. Il étale la nappe dans l'herbe, tout bas. Nino s'assoit, les pieds dans l'herbe. Le canard rond s'assoit, trop rond. Le mince s'allonge contre lui, trop mince. Vous avez le sol, tous les deux. Chacun a sa place. La nappe les abrite, tout doux. Les miettes restent, plus calmes.</t>
+          <t>L'herbe, comme une table. Il étale la nappe dans l'herbe, tout bas. Nino s'assoit, les pieds dans l'herbe. Tout doux, dans l'herbe. Le canard rond s'assoit, trop rond. Le mince s'allonge contre lui, trop mince. Vous avez le sol, tous les deux. Chacun a sa place. La nappe les abrite, tout doux. Les miettes restent, plus calmes.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>L'herbe, comme une table. Il étale la nappe dans l'herbe, tout bas. Nino s'assoit, les pieds dans l'herbe. Le canard rond s'assoit, trop rond. Le mince s'allonge contre lui, trop mince. Vous avez le sol, tous les deux. Chacun a sa place. La nappe les abrite, tout doux. Les miettes restent, plus calmes.</t>
+          <t>L'herbe, comme une table. Il étale la nappe dans l'herbe, tout bas. Nino s'assoit, les pieds dans l'herbe. Tout doux, dans l'herbe. Le canard rond s'assoit, trop rond. Le mince s'allonge contre lui, trop mince. Vous avez le sol, tous les deux. Chacun a sa place. La nappe les abrite, tout doux. Les miettes restent, plus calmes.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -9228,6 +9238,7 @@
           <t>enfant-m|L'herbe, comme une table.
 narrateur|Il étale la nappe dans l'herbe, tout bas.
 narrateur|Nino s'assoit, les pieds dans l'herbe.
+papa|Tout doux, dans l'herbe.
 narrateur|Le canard rond s'assoit, trop rond.
 narrateur|Le mince s'allonge contre lui, trop mince.
 enfant-m|Vous avez le sol, tous les deux.
@@ -10128,12 +10139,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Un coin de nappe frotte l'herbe. Au kiosque, les marches sont trop hautes. La nappe claque sur les marches, trop haut. Le goûter, là-haut. Un vent passe, tout froid. Le canard rond ne monte pas. Le mince commence, puis recule. Ils ne viennent pas. Le kiosque est trop loin de l'eau. Tu les rassembles comment ?</t>
+          <t>Un coin de nappe frotte l'herbe. Au kiosque, les marches sont trop hautes. Le goûter, là-haut. La nappe claque sur les marches, trop haut. Un vent passe, tout froid. Trop haut, trop loin. Le canard rond ne monte pas. Le mince commence, puis recule. Ils ne viennent pas. Le kiosque est trop loin de l'eau. Tu les rassembles comment ?</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Un coin de nappe frotte l'herbe. Au kiosque, les marches sont trop hautes. La nappe claque sur les marches, trop haut. Le goûter, là-haut. Un vent passe, tout froid. Le canard rond ne monte pas. Le mince commence, puis recule. Ils ne viennent pas. Le kiosque est trop loin de l'eau. Tu les rassembles comment ?</t>
+          <t>Un coin de nappe frotte l'herbe. Au kiosque, les marches sont trop hautes. Le goûter, là-haut. La nappe claque sur les marches, trop haut. Un vent passe, tout froid. Trop haut, trop loin. Le canard rond ne monte pas. Le mince commence, puis recule. Ils ne viennent pas. Le kiosque est trop loin de l'eau. Tu les rassembles comment ?</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -10270,9 +10281,10 @@
         <is>
           <t>narrateur|Un coin de nappe frotte l'herbe.
 narrateur|Au kiosque, les marches sont trop hautes.
+enfant-m|Le goûter, là-haut.
 narrateur|La nappe claque sur les marches, trop haut.
-enfant-m|Le goûter, là-haut.
 narrateur|Un vent passe, tout froid.
+maman|Trop haut, trop loin.
 narrateur|Le canard rond ne monte pas.
 narrateur|Le mince commence, puis recule.
 enfant-m|Ils ne viennent pas.
@@ -12276,12 +12288,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Le seau tape sa jambe, à chaque pas. Ils s'approchent de la mare, trop haute. Le seau penche, une miette tombe. L'eau fait un pli, trop vif. Vous venez. Le canard rond reste au bord. Le mince part, trop léger, trop loin. L'un reste, l'autre part. Ils n'ont pas la même forme. Tu fais quoi, avec les deux ?</t>
+          <t>Le seau tape sa jambe, à chaque pas. Ils s'approchent de la mare, trop haute. L'eau est grande. Le seau penche, une miette tombe. L'eau fait un pli, trop vif. Vous venez. Le canard rond reste au bord. Le mince part, trop léger, trop loin. L'un reste, l'autre part. Ils n'ont pas la même forme. Tu fais quoi, avec les deux ?</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Le seau tape sa jambe, à chaque pas. Ils s'approchent de la mare, trop haute. Le seau penche, une miette tombe. L'eau fait un pli, trop vif. Vous venez. Le canard rond reste au bord. Le mince part, trop léger, trop loin. L'un reste, l'autre part. Ils n'ont pas la même forme. Tu fais quoi, avec les deux ?</t>
+          <t>Le seau tape sa jambe, à chaque pas. Ils s'approchent de la mare, trop haute. L'eau est grande. Le seau penche, une miette tombe. L'eau fait un pli, trop vif. Vous venez. Le canard rond reste au bord. Le mince part, trop léger, trop loin. L'un reste, l'autre part. Ils n'ont pas la même forme. Tu fais quoi, avec les deux ?</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -12418,6 +12430,7 @@
         <is>
           <t>narrateur|Le seau tape sa jambe, à chaque pas.
 narrateur|Ils s'approchent de la mare, trop haute.
+enfant-m|L'eau est grande.
 narrateur|Le seau penche, une miette tombe.
 narrateur|L'eau fait un pli, trop vif.
 enfant-m|Vous venez.
@@ -13693,12 +13706,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Le seau tape sa jambe, à chaque pas. Sur le banc, les planches ont des fentes. Le seau cogne le bois, un toc. Le goûter, ici. Nino s'assoit, trop haut pour eux. Le canard rond bute, trop large. Le mince glisse entre les planches. Ce n'est pas juste. Le banc a des trous, voilà tout. Tu les gardes comment, ensemble ?</t>
+          <t>Le seau tape sa jambe, à chaque pas. Sur le banc, les planches ont des fentes. Le goûter, ici. Le seau cogne le bois, un toc. Nino s'assoit, trop haut pour eux. Tu es trop haut, pour eux. Le canard rond bute, trop large. Le mince glisse entre les planches. Ce n'est pas juste. Le banc a des trous, voilà tout. Tu les gardes comment, ensemble ?</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Le seau tape sa jambe, à chaque pas. Sur le banc, les planches ont des fentes. Le seau cogne le bois, un toc. Le goûter, ici. Nino s'assoit, trop haut pour eux. Le canard rond bute, trop large. Le mince glisse entre les planches. Ce n'est pas juste. Le banc a des trous, voilà tout. Tu les gardes comment, ensemble ?</t>
+          <t>Le seau tape sa jambe, à chaque pas. Sur le banc, les planches ont des fentes. Le goûter, ici. Le seau cogne le bois, un toc. Nino s'assoit, trop haut pour eux. Tu es trop haut, pour eux. Le canard rond bute, trop large. Le mince glisse entre les planches. Ce n'est pas juste. Le banc a des trous, voilà tout. Tu les gardes comment, ensemble ?</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -13835,9 +13848,10 @@
         <is>
           <t>narrateur|Le seau tape sa jambe, à chaque pas.
 narrateur|Sur le banc, les planches ont des fentes.
+enfant-m|Le goûter, ici.
 narrateur|Le seau cogne le bois, un toc.
-enfant-m|Le goûter, ici.
 narrateur|Nino s'assoit, trop haut pour eux.
+papa|Tu es trop haut, pour eux.
 narrateur|Le canard rond bute, trop large.
 narrateur|Le mince glisse entre les planches.
 enfant-m|Ce n'est pas juste.
@@ -14066,12 +14080,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>L'herbe, comme une table. Il pose le seau dans l'herbe, tout bas. Nino s'assoit, les pieds dans l'herbe. Le canard rond s'assoit, trop rond. Le mince s'allonge contre lui, trop mince. Vous avez le sol, tous les deux. Chacun a sa place. Un peu d'eau tremble au bord du seau. Les miettes restent, plus calmes.</t>
+          <t>L'herbe, comme une table. Il pose le seau dans l'herbe, tout bas. Nino s'assoit, les pieds dans l'herbe. Tout doux, dans l'herbe. Le canard rond s'assoit, trop rond. Le mince s'allonge contre lui, trop mince. Vous avez le sol, tous les deux. Chacun a sa place. Un peu d'eau tremble au bord du seau. Les miettes restent, plus calmes.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>L'herbe, comme une table. Il pose le seau dans l'herbe, tout bas. Nino s'assoit, les pieds dans l'herbe. Le canard rond s'assoit, trop rond. Le mince s'allonge contre lui, trop mince. Vous avez le sol, tous les deux. Chacun a sa place. Un peu d'eau tremble au bord du seau. Les miettes restent, plus calmes.</t>
+          <t>L'herbe, comme une table. Il pose le seau dans l'herbe, tout bas. Nino s'assoit, les pieds dans l'herbe. Tout doux, dans l'herbe. Le canard rond s'assoit, trop rond. Le mince s'allonge contre lui, trop mince. Vous avez le sol, tous les deux. Chacun a sa place. Un peu d'eau tremble au bord du seau. Les miettes restent, plus calmes.</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -14209,6 +14223,7 @@
           <t>enfant-m|L'herbe, comme une table.
 narrateur|Il pose le seau dans l'herbe, tout bas.
 narrateur|Nino s'assoit, les pieds dans l'herbe.
+papa|Tout doux, dans l'herbe.
 narrateur|Le canard rond s'assoit, trop rond.
 narrateur|Le mince s'allonge contre lui, trop mince.
 enfant-m|Vous avez le sol, tous les deux.
@@ -15109,12 +15124,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Le seau tape sa jambe, à chaque pas. Au kiosque, les marches sont trop hautes. Le seau tape une marche, trop haute. Le goûter, là-haut. Un vent passe, tout froid. Le canard rond ne monte pas. Le mince commence, puis recule. Ils ne viennent pas. Le kiosque est trop loin de l'eau. Tu les rassembles comment ?</t>
+          <t>Le seau tape sa jambe, à chaque pas. Au kiosque, les marches sont trop hautes. Le goûter, là-haut. Le seau tape une marche, trop haute. Un vent passe, tout froid. Trop haut, trop loin. Le canard rond ne monte pas. Le mince commence, puis recule. Ils ne viennent pas. Le kiosque est trop loin de l'eau. Tu les rassembles comment ?</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Le seau tape sa jambe, à chaque pas. Au kiosque, les marches sont trop hautes. Le seau tape une marche, trop haute. Le goûter, là-haut. Un vent passe, tout froid. Le canard rond ne monte pas. Le mince commence, puis recule. Ils ne viennent pas. Le kiosque est trop loin de l'eau. Tu les rassembles comment ?</t>
+          <t>Le seau tape sa jambe, à chaque pas. Au kiosque, les marches sont trop hautes. Le goûter, là-haut. Le seau tape une marche, trop haute. Un vent passe, tout froid. Trop haut, trop loin. Le canard rond ne monte pas. Le mince commence, puis recule. Ils ne viennent pas. Le kiosque est trop loin de l'eau. Tu les rassembles comment ?</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -15251,9 +15266,10 @@
         <is>
           <t>narrateur|Le seau tape sa jambe, à chaque pas.
 narrateur|Au kiosque, les marches sont trop hautes.
+enfant-m|Le goûter, là-haut.
 narrateur|Le seau tape une marche, trop haute.
-enfant-m|Le goûter, là-haut.
 narrateur|Un vent passe, tout froid.
+maman|Trop haut, trop loin.
 narrateur|Le canard rond ne monte pas.
 narrateur|Le mince commence, puis recule.
 enfant-m|Ils ne viennent pas.
@@ -16518,7 +16534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16561,6 +16577,13 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
